--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>127164337</v>
       </c>
       <c r="B4" t="n">
-        <v>101622</v>
+        <v>101697</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>127164338</v>
       </c>
       <c r="B5" t="n">
-        <v>106837</v>
+        <v>106912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127164336</v>
       </c>
       <c r="B6" t="n">
-        <v>88437</v>
+        <v>88505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>127164337</v>
       </c>
       <c r="B4" t="n">
-        <v>101697</v>
+        <v>101703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>127164338</v>
       </c>
       <c r="B5" t="n">
-        <v>106912</v>
+        <v>106918</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127164336</v>
       </c>
       <c r="B6" t="n">
-        <v>88505</v>
+        <v>88511</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>127164337</v>
       </c>
       <c r="B4" t="n">
-        <v>101703</v>
+        <v>101704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>127164338</v>
       </c>
       <c r="B5" t="n">
-        <v>106918</v>
+        <v>106919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127164336</v>
       </c>
       <c r="B6" t="n">
-        <v>88511</v>
+        <v>88512</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>127164337</v>
       </c>
       <c r="B4" t="n">
-        <v>101704</v>
+        <v>101708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>127164338</v>
       </c>
       <c r="B5" t="n">
-        <v>106919</v>
+        <v>106925</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127164336</v>
       </c>
       <c r="B6" t="n">
-        <v>88512</v>
+        <v>88516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>127164337</v>
       </c>
       <c r="B4" t="n">
-        <v>101708</v>
+        <v>101709</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>127164338</v>
       </c>
       <c r="B5" t="n">
-        <v>106925</v>
+        <v>106927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>127164337</v>
       </c>
       <c r="B4" t="n">
-        <v>101709</v>
+        <v>101711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>127164338</v>
       </c>
       <c r="B5" t="n">
-        <v>106927</v>
+        <v>106929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127164336</v>
       </c>
       <c r="B6" t="n">
-        <v>88516</v>
+        <v>88518</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>127164337</v>
       </c>
       <c r="B4" t="n">
-        <v>101711</v>
+        <v>101717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>127164338</v>
       </c>
       <c r="B5" t="n">
-        <v>106929</v>
+        <v>106935</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127164336</v>
       </c>
       <c r="B6" t="n">
-        <v>88518</v>
+        <v>88524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>127164337</v>
       </c>
       <c r="B4" t="n">
-        <v>101717</v>
+        <v>101720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>127164338</v>
       </c>
       <c r="B5" t="n">
-        <v>106935</v>
+        <v>106938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127164336</v>
       </c>
       <c r="B6" t="n">
-        <v>88524</v>
+        <v>88527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>127164337</v>
       </c>
       <c r="B4" t="n">
-        <v>101720</v>
+        <v>101728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>127164338</v>
       </c>
       <c r="B5" t="n">
-        <v>106938</v>
+        <v>106946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>127164336</v>
       </c>
       <c r="B6" t="n">
-        <v>88527</v>
+        <v>88535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>127164337</v>
       </c>
       <c r="B4" t="n">
-        <v>101728</v>
+        <v>101729</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Edelsjö, Kristoffer Stighäll, Isak Isaksson</t>
+          <t>Isak Isaksson, Kristoffer Stighäll, Jan Edelsjö</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
         <v>127164338</v>
       </c>
       <c r="B5" t="n">
-        <v>106946</v>
+        <v>106947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Edelsjö, Kristoffer Stighäll, Isak Isaksson</t>
+          <t>Isak Isaksson, Kristoffer Stighäll, Jan Edelsjö</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1149,7 +1149,7 @@
         <v>127164336</v>
       </c>
       <c r="B6" t="n">
-        <v>88535</v>
+        <v>88536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Edelsjö, Kristoffer Stighäll, Isak Isaksson</t>
+          <t>Isak Isaksson, Kristoffer Stighäll, Jan Edelsjö</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,6 +1251,137 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128925661</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101900</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Blåkullavägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>693081</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6659488</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka ex ännu i blom.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Skogsbilvägren</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>128925661</v>
       </c>
       <c r="B7" t="n">
-        <v>101900</v>
+        <v>101904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>128925661</v>
       </c>
       <c r="B7" t="n">
-        <v>101904</v>
+        <v>101911</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>128925661</v>
       </c>
       <c r="B7" t="n">
-        <v>101919</v>
+        <v>101924</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>128925661</v>
       </c>
       <c r="B7" t="n">
-        <v>101924</v>
+        <v>101927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>128925661</v>
       </c>
       <c r="B7" t="n">
-        <v>101927</v>
+        <v>101937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>128925661</v>
       </c>
       <c r="B7" t="n">
-        <v>101937</v>
+        <v>101944</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>128925661</v>
       </c>
       <c r="B7" t="n">
-        <v>101944</v>
+        <v>101946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>128925661</v>
       </c>
       <c r="B7" t="n">
-        <v>101946</v>
+        <v>101972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>128925661</v>
       </c>
       <c r="B7" t="n">
-        <v>101972</v>
+        <v>101974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>128925661</v>
       </c>
       <c r="B7" t="n">
-        <v>101974</v>
+        <v>101975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>128925661</v>
       </c>
       <c r="B7" t="n">
-        <v>101975</v>
+        <v>101979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>128925661</v>
       </c>
       <c r="B7" t="n">
-        <v>101979</v>
+        <v>101981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>128925661</v>
       </c>
       <c r="B7" t="n">
-        <v>101981</v>
+        <v>101985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>127164337</v>
       </c>
       <c r="B4" t="n">
-        <v>101729</v>
+        <v>101697</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isak Isaksson, Kristoffer Stighäll, Jan Edelsjö</t>
+          <t>Jan Edelsjö, Kristoffer Stighäll, Isak Isaksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
         <v>127164338</v>
       </c>
       <c r="B5" t="n">
-        <v>106947</v>
+        <v>106912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Isaksson, Kristoffer Stighäll, Jan Edelsjö</t>
+          <t>Jan Edelsjö, Kristoffer Stighäll, Isak Isaksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1149,7 +1149,7 @@
         <v>127164336</v>
       </c>
       <c r="B6" t="n">
-        <v>88536</v>
+        <v>88505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Isaksson, Kristoffer Stighäll, Jan Edelsjö</t>
+          <t>Jan Edelsjö, Kristoffer Stighäll, Isak Isaksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 15804-2025 artfynd.xlsx
+++ b/artfynd/A 15804-2025 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>127164337</v>
       </c>
       <c r="B4" t="n">
-        <v>101697</v>
+        <v>101729</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Edelsjö, Kristoffer Stighäll, Isak Isaksson</t>
+          <t>Isak Isaksson, Kristoffer Stighäll, Jan Edelsjö</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
         <v>127164338</v>
       </c>
       <c r="B5" t="n">
-        <v>106912</v>
+        <v>106947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Edelsjö, Kristoffer Stighäll, Isak Isaksson</t>
+          <t>Isak Isaksson, Kristoffer Stighäll, Jan Edelsjö</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1149,7 +1149,7 @@
         <v>127164336</v>
       </c>
       <c r="B6" t="n">
-        <v>88505</v>
+        <v>88536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Edelsjö, Kristoffer Stighäll, Isak Isaksson</t>
+          <t>Isak Isaksson, Kristoffer Stighäll, Jan Edelsjö</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
